--- a/Constraint_dataset.xlsx
+++ b/Constraint_dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Documents\NX_Journals\September_2025\29.09.2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Documents\NX_Journals\Oktober_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA2E738-8411-48ED-BB3F-AE072969BEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4658853E-CEC6-4603-BF51-3299581AE295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="603" xr2:uid="{20B34EDE-9914-46DA-B464-CD7B7E420491}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="171">
   <si>
     <t>Part1</t>
   </si>
@@ -189,9 +189,6 @@
     <t>Cylinder_displacement3</t>
   </si>
   <si>
-    <t>rod</t>
-  </si>
-  <si>
     <t>Crank_nub</t>
   </si>
   <si>
@@ -247,12 +244,6 @@
   </si>
   <si>
     <t>SPUR_GEAR_12</t>
-  </si>
-  <si>
-    <t>SCREW SHAFT</t>
-  </si>
-  <si>
-    <t>E-RING EXTERNAL RETAINING RING</t>
   </si>
   <si>
     <t>SHAFT_12MM_SCREW</t>
@@ -312,49 +303,13 @@
     <t>Align_Cone_Cone</t>
   </si>
   <si>
-    <t>WELL CASING</t>
-  </si>
-  <si>
-    <t>WELL SEAL</t>
-  </si>
-  <si>
-    <t>PIVOT SUPPORT</t>
-  </si>
-  <si>
-    <t>PUMP BASE</t>
-  </si>
-  <si>
     <t>TEE</t>
-  </si>
-  <si>
-    <t>GUIDE CYLINDER</t>
-  </si>
-  <si>
-    <t>STROKE SLIDE</t>
-  </si>
-  <si>
-    <t>OUTPUT PIPE</t>
-  </si>
-  <si>
-    <t>PIVOT BLOCK</t>
-  </si>
-  <si>
-    <t>OFFSET LINK</t>
   </si>
   <si>
     <t>InPlane</t>
   </si>
   <si>
-    <t>24 MM NUT</t>
-  </si>
-  <si>
     <t>HANDLE</t>
-  </si>
-  <si>
-    <t>30 MM BOLT</t>
-  </si>
-  <si>
-    <t>30 MM NUT</t>
   </si>
   <si>
     <t>cylinder</t>
@@ -529,6 +484,72 @@
   </si>
   <si>
     <t>M6_set_screw</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>crank</t>
+  </si>
+  <si>
+    <t>bearing</t>
+  </si>
+  <si>
+    <t>bolt</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>piston</t>
+  </si>
+  <si>
+    <t>blot</t>
+  </si>
+  <si>
+    <t>E-RING_EXTERNAL_RETAINING_RING</t>
+  </si>
+  <si>
+    <t>WELL_CASING</t>
+  </si>
+  <si>
+    <t>WELL_SEAL</t>
+  </si>
+  <si>
+    <t>PIVOT_SUPPORT</t>
+  </si>
+  <si>
+    <t>PUMP_BASE</t>
+  </si>
+  <si>
+    <t>GUIDE_CYLINDER</t>
+  </si>
+  <si>
+    <t>STROKE_SLIDE</t>
+  </si>
+  <si>
+    <t>OUTPUT_PIPE</t>
+  </si>
+  <si>
+    <t>PIVOT_BLOCK</t>
+  </si>
+  <si>
+    <t>OFFSET_LINK</t>
+  </si>
+  <si>
+    <t>24_MM_NUT</t>
+  </si>
+  <si>
+    <t>30_MM_BOLT</t>
+  </si>
+  <si>
+    <t>30_MM_NUT</t>
+  </si>
+  <si>
+    <t>LOADCELL</t>
   </si>
 </sst>
 </file>
@@ -970,13 +991,13 @@
         <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>39</v>
@@ -985,16 +1006,16 @@
         <v>40</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>2</v>
@@ -1009,37 +1030,37 @@
         <v>44</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>7</v>
@@ -1088,7 +1109,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -2299,8 +2320,8 @@
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
+      <c r="D11" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -2561,10 +2582,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -2693,10 +2714,10 @@
         <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -2824,11 +2845,11 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="1">
-        <v>0</v>
+      <c r="C15" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -2956,11 +2977,11 @@
       <c r="B16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="1">
-        <v>0</v>
+      <c r="C16" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -3088,11 +3109,11 @@
       <c r="B17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="1">
-        <v>0</v>
+      <c r="C17" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -3220,11 +3241,11 @@
       <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="1">
-        <v>0</v>
+      <c r="C18" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
@@ -3352,11 +3373,11 @@
       <c r="B19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="1">
-        <v>0</v>
+      <c r="C19" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
@@ -3482,13 +3503,13 @@
         <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -3617,10 +3638,10 @@
         <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -3749,10 +3770,10 @@
         <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -3881,10 +3902,10 @@
         <v>48</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -4013,10 +4034,10 @@
         <v>48</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -4145,10 +4166,10 @@
         <v>48</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -4276,11 +4297,11 @@
       <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
+      <c r="C26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -4408,11 +4429,11 @@
       <c r="B27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
+      <c r="C27" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -4540,11 +4561,11 @@
       <c r="B28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
+      <c r="C28" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -4672,11 +4693,11 @@
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
+      <c r="C29" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -4804,11 +4825,11 @@
       <c r="B30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
+      <c r="C30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -4936,11 +4957,11 @@
       <c r="B31" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
+      <c r="C31" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -5063,16 +5084,16 @@
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C32" s="1">
         <v>1</v>
       </c>
-      <c r="D32" s="1">
-        <v>0</v>
+      <c r="D32" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5195,16 +5216,16 @@
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="C33" s="1">
         <v>0</v>
       </c>
-      <c r="D33" s="1">
-        <v>0</v>
+      <c r="D33" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
@@ -5327,10 +5348,10 @@
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
@@ -5461,10 +5482,10 @@
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
@@ -5595,10 +5616,10 @@
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>26</v>
@@ -5729,7 +5750,7 @@
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>15</v>
@@ -5863,13 +5884,13 @@
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0</v>
+      <c r="C38" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>25</v>
@@ -5995,13 +6016,13 @@
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -6127,13 +6148,13 @@
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -6259,16 +6280,16 @@
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6391,10 +6412,10 @@
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>25</v>
@@ -6523,16 +6544,16 @@
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
+      <c r="D43" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -6655,10 +6676,10 @@
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="1">
         <v>0</v>
@@ -6787,10 +6808,10 @@
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C45" s="1">
         <v>0</v>
@@ -6919,16 +6940,16 @@
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -7053,13 +7074,13 @@
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -7187,13 +7208,13 @@
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -7321,13 +7342,13 @@
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>15</v>
@@ -7455,10 +7476,10 @@
     </row>
     <row r="50" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>15</v>
@@ -7589,16 +7610,16 @@
     </row>
     <row r="51" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
+      <c r="D51" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -7723,16 +7744,16 @@
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
+      <c r="D52" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -7857,16 +7878,16 @@
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
+      <c r="D53" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -7991,10 +8012,10 @@
     </row>
     <row r="54" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>15</v>
@@ -8125,16 +8146,16 @@
     </row>
     <row r="55" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0</v>
-      </c>
-      <c r="D55" s="1">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -8259,16 +8280,16 @@
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0</v>
-      </c>
-      <c r="D56" s="1">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -8393,13 +8414,13 @@
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -8527,16 +8548,16 @@
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0</v>
-      </c>
-      <c r="D58" s="1">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -8661,13 +8682,13 @@
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>15</v>
@@ -8795,10 +8816,10 @@
     </row>
     <row r="60" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C60" s="1">
         <v>0</v>
@@ -8929,10 +8950,10 @@
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C61" s="1">
         <v>0</v>
@@ -9063,10 +9084,10 @@
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -9197,10 +9218,10 @@
     </row>
     <row r="63" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="C63" s="1">
         <v>0</v>
@@ -9331,16 +9352,16 @@
     </row>
     <row r="64" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="C64" s="1">
         <v>0</v>
       </c>
-      <c r="D64" s="1">
-        <v>0</v>
+      <c r="D64" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -9465,10 +9486,10 @@
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C65" s="1">
         <v>0</v>
@@ -9599,16 +9620,16 @@
     </row>
     <row r="66" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
       </c>
-      <c r="D66" s="1">
-        <v>0</v>
+      <c r="D66" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -9733,16 +9754,16 @@
     </row>
     <row r="67" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="C67" s="1">
         <v>0</v>
       </c>
-      <c r="D67" s="1">
-        <v>0</v>
+      <c r="D67" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -9867,10 +9888,10 @@
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
@@ -10001,10 +10022,10 @@
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="C69" s="1">
         <v>0</v>
@@ -10135,13 +10156,13 @@
     </row>
     <row r="70" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
@@ -10269,10 +10290,10 @@
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="C71" s="1">
         <v>0</v>
@@ -10403,10 +10424,10 @@
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
@@ -10532,15 +10553,15 @@
         <v>1</v>
       </c>
       <c r="AR72" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1">
         <v>0</v>
@@ -10666,21 +10687,21 @@
         <v>1</v>
       </c>
       <c r="AR73" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="C74" s="1">
         <v>0</v>
       </c>
-      <c r="D74" s="1">
-        <v>0</v>
+      <c r="D74" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -10805,16 +10826,16 @@
     </row>
     <row r="75" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="C75" s="1">
         <v>0</v>
       </c>
-      <c r="D75" s="1">
-        <v>0</v>
+      <c r="D75" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -10939,10 +10960,10 @@
     </row>
     <row r="76" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C76" s="1">
         <v>0</v>
@@ -11073,10 +11094,10 @@
     </row>
     <row r="77" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C77" s="1">
         <v>0</v>
@@ -11207,10 +11228,10 @@
     </row>
     <row r="78" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="C78" s="1">
         <v>0</v>
@@ -11341,10 +11362,10 @@
     </row>
     <row r="79" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C79" s="1">
         <v>0</v>
@@ -11475,16 +11496,16 @@
     </row>
     <row r="80" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
       </c>
-      <c r="D80" s="1">
-        <v>0</v>
+      <c r="D80" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -11609,16 +11630,16 @@
     </row>
     <row r="81" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="C81" s="1">
         <v>0</v>
       </c>
-      <c r="D81" s="1">
-        <v>0</v>
+      <c r="D81" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -11743,16 +11764,16 @@
     </row>
     <row r="82" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="C82" s="1">
         <v>0</v>
       </c>
-      <c r="D82" s="1">
-        <v>0</v>
+      <c r="D82" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -11877,16 +11898,16 @@
     </row>
     <row r="83" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="C83" s="1">
         <v>0</v>
       </c>
-      <c r="D83" s="1">
-        <v>0</v>
+      <c r="D83" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -12011,16 +12032,16 @@
     </row>
     <row r="84" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="C84" s="1">
         <v>0</v>
       </c>
-      <c r="D84" s="1">
-        <v>0</v>
+      <c r="D84" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -12145,16 +12166,16 @@
     </row>
     <row r="85" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="C85" s="1">
         <v>0</v>
       </c>
-      <c r="D85" s="1">
-        <v>0</v>
+      <c r="D85" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -12279,16 +12300,16 @@
     </row>
     <row r="86" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="C86" s="1">
         <v>0</v>
       </c>
-      <c r="D86" s="1">
-        <v>0</v>
+      <c r="D86" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
@@ -12413,16 +12434,16 @@
     </row>
     <row r="87" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
       </c>
-      <c r="D87" s="1">
-        <v>0</v>
+      <c r="D87" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -12547,10 +12568,10 @@
     </row>
     <row r="88" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
@@ -12681,10 +12702,10 @@
     </row>
     <row r="89" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C89" s="1">
         <v>0</v>
@@ -12815,10 +12836,10 @@
     </row>
     <row r="90" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
@@ -12949,10 +12970,10 @@
     </row>
     <row r="91" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C91" s="1">
         <v>0</v>
@@ -13083,10 +13104,10 @@
     </row>
     <row r="92" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C92" s="1">
         <v>0</v>
@@ -13217,10 +13238,10 @@
     </row>
     <row r="93" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
@@ -13351,13 +13372,13 @@
     </row>
     <row r="94" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>25</v>
@@ -13485,13 +13506,13 @@
     </row>
     <row r="95" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C95" s="1">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>25</v>
@@ -13619,13 +13640,13 @@
     </row>
     <row r="96" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>25</v>
@@ -13753,13 +13774,13 @@
     </row>
     <row r="97" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>25</v>
@@ -13887,13 +13908,13 @@
     </row>
     <row r="98" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C98" s="1">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>25</v>
@@ -14021,13 +14042,13 @@
     </row>
     <row r="99" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C99" s="1">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>25</v>
@@ -14155,13 +14176,13 @@
     </row>
     <row r="100" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C100" s="1">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>25</v>
@@ -14289,13 +14310,13 @@
     </row>
     <row r="101" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>25</v>
@@ -14309,8 +14330,8 @@
       <c r="G101" s="1">
         <v>0</v>
       </c>
-      <c r="H101" s="1">
-        <v>0</v>
+      <c r="H101" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="I101" s="1">
         <v>0</v>
@@ -14423,13 +14444,13 @@
     </row>
     <row r="102" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C102" s="1">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>25</v>
@@ -14557,13 +14578,13 @@
     </row>
     <row r="103" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>25</v>
@@ -14691,13 +14712,13 @@
     </row>
     <row r="104" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C104" s="1">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>25</v>
@@ -14825,13 +14846,13 @@
     </row>
     <row r="105" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>25</v>
@@ -14959,13 +14980,13 @@
     </row>
     <row r="106" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C106" s="1">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
@@ -15093,10 +15114,10 @@
     </row>
     <row r="107" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
@@ -15228,10 +15249,10 @@
     </row>
     <row r="108" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
@@ -15365,13 +15386,13 @@
         <v>46</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0</v>
-      </c>
-      <c r="D109" s="1">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
@@ -15499,11 +15520,11 @@
       <c r="B110" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C110" s="1">
-        <v>0</v>
-      </c>
-      <c r="D110" s="1">
-        <v>0</v>
+      <c r="C110" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
@@ -15626,16 +15647,16 @@
     </row>
     <row r="111" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C111" s="1">
-        <v>0</v>
-      </c>
-      <c r="D111" s="1">
-        <v>0</v>
+      <c r="C111" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -15758,16 +15779,16 @@
     </row>
     <row r="112" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0</v>
-      </c>
-      <c r="D112" s="1">
-        <v>0</v>
+        <v>104</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -15895,11 +15916,11 @@
       <c r="B113" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C113" s="1">
-        <v>0</v>
-      </c>
-      <c r="D113" s="1">
-        <v>0</v>
+      <c r="C113" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -16025,13 +16046,13 @@
         <v>48</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C114" s="1">
-        <v>0</v>
-      </c>
-      <c r="D114" s="1">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -16157,13 +16178,13 @@
         <v>48</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -16286,16 +16307,16 @@
     </row>
     <row r="116" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E116" s="1">
         <v>2</v>
@@ -16415,21 +16436,21 @@
         <v>4</v>
       </c>
       <c r="AR116" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
@@ -16549,21 +16570,21 @@
         <v>1</v>
       </c>
       <c r="AR117" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
@@ -16686,16 +16707,16 @@
     </row>
     <row r="119" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
@@ -16818,16 +16839,16 @@
     </row>
     <row r="120" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
@@ -16950,16 +16971,16 @@
     </row>
     <row r="121" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
@@ -17082,13 +17103,13 @@
     </row>
     <row r="122" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
@@ -17214,16 +17235,16 @@
     </row>
     <row r="123" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
@@ -17346,13 +17367,13 @@
     </row>
     <row r="124" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C124" s="1">
-        <v>0</v>
+        <v>116</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
@@ -17478,13 +17499,13 @@
     </row>
     <row r="125" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C125" s="1">
-        <v>0</v>
+        <v>117</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
@@ -17605,19 +17626,19 @@
         <v>1</v>
       </c>
       <c r="AR125" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="AT125" s="2"/>
     </row>
     <row r="126" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C126" s="1">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
@@ -17743,13 +17764,13 @@
     </row>
     <row r="127" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C127" s="1">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
@@ -17875,13 +17896,13 @@
     </row>
     <row r="128" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C128" s="1">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
@@ -18007,13 +18028,13 @@
     </row>
     <row r="129" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
@@ -18139,13 +18160,13 @@
     </row>
     <row r="130" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C130" s="1">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
@@ -18271,13 +18292,13 @@
     </row>
     <row r="131" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0</v>
+        <v>127</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
@@ -18403,10 +18424,10 @@
     </row>
     <row r="132" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C132" s="1">
         <v>0</v>
@@ -18535,10 +18556,10 @@
     </row>
     <row r="133" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -18667,10 +18688,10 @@
     </row>
     <row r="134" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -18799,10 +18820,10 @@
     </row>
     <row r="135" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C135" s="1">
         <v>0</v>
@@ -18931,10 +18952,10 @@
     </row>
     <row r="136" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C136" s="1">
         <v>0</v>
@@ -19063,10 +19084,10 @@
     </row>
     <row r="137" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C137" s="1">
         <v>0</v>
@@ -19195,10 +19216,10 @@
     </row>
     <row r="138" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
@@ -19327,10 +19348,10 @@
     </row>
     <row r="139" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C139" s="1">
         <v>0</v>
@@ -19459,10 +19480,10 @@
     </row>
     <row r="140" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C140" s="1">
         <v>0</v>
@@ -19591,10 +19612,10 @@
     </row>
     <row r="141" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C141" s="1">
         <v>0</v>
@@ -19718,15 +19739,15 @@
         <v>2</v>
       </c>
       <c r="AR141" s="1" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="142" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C142" s="1">
         <v>0</v>
@@ -19855,10 +19876,10 @@
     </row>
     <row r="143" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -19989,10 +20010,10 @@
     </row>
     <row r="144" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C144" s="1">
         <v>0</v>
@@ -20123,16 +20144,16 @@
     </row>
     <row r="145" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C145" s="1">
-        <v>0</v>
-      </c>
-      <c r="D145" s="1">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E145" s="1">
         <v>1</v>
@@ -20257,16 +20278,16 @@
     </row>
     <row r="146" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C146" s="1">
-        <v>0</v>
-      </c>
-      <c r="D146" s="1">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E146" s="1">
         <v>1</v>
@@ -20391,16 +20412,16 @@
     </row>
     <row r="147" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C147" s="1">
-        <v>0</v>
-      </c>
-      <c r="D147" s="1">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E147" s="1">
         <v>0</v>
@@ -20525,16 +20546,16 @@
     </row>
     <row r="148" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C148" s="1">
-        <v>0</v>
-      </c>
-      <c r="D148" s="1">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
@@ -20659,16 +20680,16 @@
     </row>
     <row r="149" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C149" s="1">
-        <v>0</v>
-      </c>
-      <c r="D149" s="1">
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -20793,16 +20814,16 @@
     </row>
     <row r="150" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C150" s="1">
-        <v>0</v>
-      </c>
-      <c r="D150" s="1">
-        <v>0</v>
+        <v>140</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -20927,13 +20948,13 @@
     </row>
     <row r="151" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C151" s="1">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D151" s="1">
         <v>0</v>
@@ -21061,10 +21082,10 @@
     </row>
     <row r="152" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C152" s="1">
         <v>0</v>
@@ -21195,10 +21216,10 @@
     </row>
     <row r="153" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C153" s="1">
         <v>0</v>
@@ -21329,10 +21350,10 @@
     </row>
     <row r="154" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C154" s="1">
         <v>0</v>
@@ -21463,16 +21484,16 @@
     </row>
     <row r="155" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C155" s="1">
         <v>0</v>
       </c>
-      <c r="D155" s="1">
-        <v>0</v>
+      <c r="D155" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E155" s="1">
         <v>0</v>
